--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SCL.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SCL.xlsx
@@ -1185,7 +1185,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -1871,7 +1875,11 @@
           <t>SCL_V._MARKOVETSKYY</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>323157</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>V. Markovetskyy</t>
@@ -2573,7 +2581,11 @@
           <t>SCL_J._COSTA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>209330</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>J. Costa</t>
@@ -3401,7 +3413,11 @@
           <t>SCL_V._MARKOVETSKYY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>323157</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>V. Markovetskyy</t>
@@ -3871,7 +3887,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -5263,7 +5283,11 @@
           <t>SCL_J._COSTA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>209330</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>J. Costa</t>
@@ -5869,7 +5893,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -6601,7 +6629,11 @@
           <t>SCL_J._COSTA</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>209330</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>J. Costa</t>
@@ -7283,7 +7315,11 @@
           <t>SCL_V._MARKOVETSKYY</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>323157</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>V. Markovetskyy</t>
@@ -8337,7 +8373,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -9069,7 +9109,11 @@
           <t>SCL_J._COSTA</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>209330</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>J. Costa</t>
@@ -10654,7 +10698,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -10944,7 +10992,11 @@
           <t>SCL_V._MARKOVETSKYY</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>323157</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>V. Markovetskyy</t>
@@ -11332,7 +11384,11 @@
           <t>SCL_J._COSTA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>209330</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>J. Costa</t>
@@ -11426,7 +11482,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -11618,7 +11678,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -11908,7 +11972,11 @@
           <t>SCL_V._MARKOVETSKYY</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>323157</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>V. Markovetskyy</t>
@@ -12164,7 +12232,11 @@
           <t>SCL_V._MARKOVETSKYY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>323157</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>V. Markovetskyy</t>
@@ -12552,7 +12624,11 @@
           <t>SCL_S._EVANS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>323155</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>S. Evans</t>
@@ -12842,7 +12918,11 @@
           <t>SCL_J._COSTA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>209330</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>J. Costa</t>
